--- a/Article Charts/peru/Chartbook_Peru_Critical Minerals_LMC&TC_v1.xlsx
+++ b/Article Charts/peru/Chartbook_Peru_Critical Minerals_LMC&TC_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tiffanylam/Desktop/LSE/Year 2/Growth Lab/RADataHub/Article Charts/peru/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F712F187-49E8-BD4E-909F-08C979BEB8A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{044446A6-8C74-1248-801E-0F4743E96E8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28960" yWindow="660" windowWidth="18980" windowHeight="20780" xr2:uid="{870548DC-9C05-4490-94E9-602C6F3D4CF6}"/>
+    <workbookView xWindow="28960" yWindow="660" windowWidth="18980" windowHeight="20780" activeTab="1" xr2:uid="{870548DC-9C05-4490-94E9-602C6F3D4CF6}"/>
   </bookViews>
   <sheets>
     <sheet name="Chart 1" sheetId="5" r:id="rId1"/>
